--- a/outputs/M5_lending_rate_robustness_regression_detail.xlsx
+++ b/outputs/M5_lending_rate_robustness_regression_detail.xlsx
@@ -40,22 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>lending_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>inflation_gdp_deflator_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
 </sst>
 </file>
@@ -447,19 +447,19 @@
         <v>56.52953860726176</v>
       </c>
       <c r="C2">
-        <v>34.77226836236632</v>
+        <v>34.77226836235302</v>
       </c>
       <c r="D2">
-        <v>1.62570753274305</v>
+        <v>1.625707532743672</v>
       </c>
       <c r="E2">
-        <v>0.1085060383332521</v>
+        <v>0.1085060383331193</v>
       </c>
       <c r="F2">
-        <v>-12.82156387510872</v>
+        <v>-12.8215638750822</v>
       </c>
       <c r="G2">
-        <v>125.8806410896322</v>
+        <v>125.8806410896057</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.04968848428350695</v>
+        <v>0.03233741312401193</v>
       </c>
       <c r="C3">
-        <v>0.06045074003287915</v>
+        <v>0.0788216925936376</v>
       </c>
       <c r="D3">
-        <v>0.8219665178041062</v>
+        <v>0.410260323775668</v>
       </c>
       <c r="E3">
-        <v>0.4138869549619693</v>
+        <v>0.6828679862170266</v>
       </c>
       <c r="F3">
-        <v>-0.07087671507209936</v>
+        <v>-0.1248674957973589</v>
       </c>
       <c r="G3">
-        <v>0.1702536836391133</v>
+        <v>0.1895423220453828</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.9683603068768689</v>
+        <v>-0.05466996868666928</v>
       </c>
       <c r="C4">
-        <v>0.3466622498138464</v>
+        <v>0.0220918352842307</v>
       </c>
       <c r="D4">
-        <v>-2.793382629336962</v>
+        <v>-2.474668491019082</v>
       </c>
       <c r="E4">
-        <v>0.006722210589746647</v>
+        <v>0.01576157741089235</v>
       </c>
       <c r="F4">
-        <v>-1.659756363155698</v>
+        <v>-0.09873074484467513</v>
       </c>
       <c r="G4">
-        <v>-0.2769642505980398</v>
+        <v>-0.01060919252866344</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.03233741312401189</v>
+        <v>-4.841282139630158</v>
       </c>
       <c r="C5">
-        <v>0.07882169259364138</v>
+        <v>3.99387049889693</v>
       </c>
       <c r="D5">
-        <v>0.4102603237756477</v>
+        <v>-1.212178046575941</v>
       </c>
       <c r="E5">
-        <v>0.6828679862170413</v>
+        <v>0.2295198196796655</v>
       </c>
       <c r="F5">
-        <v>-0.1248674957973665</v>
+        <v>-12.8068056822383</v>
       </c>
       <c r="G5">
-        <v>0.1895423220453903</v>
+        <v>3.124241402977981</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-0.05466996868666922</v>
+        <v>0.1147033457445316</v>
       </c>
       <c r="C6">
-        <v>0.02209183528423128</v>
+        <v>0.09923773777214236</v>
       </c>
       <c r="D6">
-        <v>-2.474668491019013</v>
+        <v>1.155844019821365</v>
       </c>
       <c r="E6">
-        <v>0.01576157741089523</v>
+        <v>0.2516748367302015</v>
       </c>
       <c r="F6">
-        <v>-0.09873074484467624</v>
+        <v>-0.08322008135644636</v>
       </c>
       <c r="G6">
-        <v>-0.0106091925286622</v>
+        <v>0.3126267728455095</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>-4.841282139630157</v>
+        <v>0.04968848428350701</v>
       </c>
       <c r="C7">
-        <v>3.993870498898322</v>
+        <v>0.06045074003288377</v>
       </c>
       <c r="D7">
-        <v>-1.212178046575518</v>
+        <v>0.8219665178040444</v>
       </c>
       <c r="E7">
-        <v>0.2295198196798263</v>
+        <v>0.4138869549620041</v>
       </c>
       <c r="F7">
-        <v>-12.80680568224107</v>
+        <v>-0.07087671507210851</v>
       </c>
       <c r="G7">
-        <v>3.124241402980759</v>
+        <v>0.1702536836391225</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.1147033457445316</v>
+        <v>-0.9683603068768686</v>
       </c>
       <c r="C8">
-        <v>0.09923773777214391</v>
+        <v>0.3466622498137921</v>
       </c>
       <c r="D8">
-        <v>1.155844019821348</v>
+        <v>-2.793382629337398</v>
       </c>
       <c r="E8">
-        <v>0.2516748367302086</v>
+        <v>0.006722210589738653</v>
       </c>
       <c r="F8">
-        <v>-0.0832200813564494</v>
+        <v>-1.659756363155589</v>
       </c>
       <c r="G8">
-        <v>0.3126267728455127</v>
+        <v>-0.2769642505981478</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M5_lending_rate_robustness_regression_detail.xlsx
+++ b/outputs/M5_lending_rate_robustness_regression_detail.xlsx
@@ -40,6 +40,12 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>broad_money_growth_pct</t>
+  </si>
+  <si>
+    <t>lending_interest_rate_pct</t>
+  </si>
+  <si>
     <t>inflation_gdp_deflator_pct</t>
   </si>
   <si>
@@ -50,12 +56,6 @@
   </si>
   <si>
     <t>xr_dep_pct</t>
-  </si>
-  <si>
-    <t>broad_money_pct_gdp</t>
-  </si>
-  <si>
-    <t>lending_interest_rate_pct</t>
   </si>
 </sst>
 </file>
@@ -444,22 +444,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>56.52953860726176</v>
+        <v>-43.46557374134938</v>
       </c>
       <c r="C2">
-        <v>34.77226836235302</v>
+        <v>14.86976661920709</v>
       </c>
       <c r="D2">
-        <v>1.625707532743672</v>
+        <v>-2.923083788363258</v>
       </c>
       <c r="E2">
-        <v>0.1085060383331193</v>
+        <v>0.004168010854836313</v>
       </c>
       <c r="F2">
-        <v>-12.8215638750822</v>
+        <v>-72.91702015732643</v>
       </c>
       <c r="G2">
-        <v>125.8806410896057</v>
+        <v>-14.01412732537233</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.03233741312401193</v>
+        <v>0.06270990124607147</v>
       </c>
       <c r="C3">
-        <v>0.0788216925936376</v>
+        <v>0.03603915795583157</v>
       </c>
       <c r="D3">
-        <v>0.410260323775668</v>
+        <v>1.740049013434962</v>
       </c>
       <c r="E3">
-        <v>0.6828679862170266</v>
+        <v>0.08450252994080842</v>
       </c>
       <c r="F3">
-        <v>-0.1248674957973589</v>
+        <v>-0.008670192106712049</v>
       </c>
       <c r="G3">
-        <v>0.1895423220453828</v>
+        <v>0.134089994598855</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.05466996868666928</v>
+        <v>0.2499853006579213</v>
       </c>
       <c r="C4">
-        <v>0.0220918352842307</v>
+        <v>0.1738227271094773</v>
       </c>
       <c r="D4">
-        <v>-2.474668491019082</v>
+        <v>1.438162343986671</v>
       </c>
       <c r="E4">
-        <v>0.01576157741089235</v>
+        <v>0.1530804333689331</v>
       </c>
       <c r="F4">
-        <v>-0.09873074484467513</v>
+        <v>-0.09429251246734965</v>
       </c>
       <c r="G4">
-        <v>-0.01060919252866344</v>
+        <v>0.5942631137831922</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-4.841282139630158</v>
+        <v>-0.01999031127954806</v>
       </c>
       <c r="C5">
-        <v>3.99387049889693</v>
+        <v>0.03962312892954337</v>
       </c>
       <c r="D5">
-        <v>-1.212178046575941</v>
+        <v>-0.5045111736403809</v>
       </c>
       <c r="E5">
-        <v>0.2295198196796655</v>
+        <v>0.6148592248372982</v>
       </c>
       <c r="F5">
-        <v>-12.8068056822383</v>
+        <v>-0.09846891073479783</v>
       </c>
       <c r="G5">
-        <v>3.124241402977981</v>
+        <v>0.05848828817570171</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.1147033457445316</v>
+        <v>-0.01819387271369492</v>
       </c>
       <c r="C6">
-        <v>0.09923773777214236</v>
+        <v>0.01672232719159006</v>
       </c>
       <c r="D6">
-        <v>1.155844019821365</v>
+        <v>-1.087998847603277</v>
       </c>
       <c r="E6">
-        <v>0.2516748367302015</v>
+        <v>0.2788510036563399</v>
       </c>
       <c r="F6">
-        <v>-0.08322008135644636</v>
+        <v>-0.05131454877039905</v>
       </c>
       <c r="G6">
-        <v>0.3126267728455095</v>
+        <v>0.01492680334300921</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.04968848428350701</v>
+        <v>1.881515705453273</v>
       </c>
       <c r="C7">
-        <v>0.06045074003288377</v>
+        <v>0.5927886930141817</v>
       </c>
       <c r="D7">
-        <v>0.8219665178040444</v>
+        <v>3.174007412128997</v>
       </c>
       <c r="E7">
-        <v>0.4138869549620041</v>
+        <v>0.001925345492274078</v>
       </c>
       <c r="F7">
-        <v>-0.07087671507210851</v>
+        <v>0.7074230061264839</v>
       </c>
       <c r="G7">
-        <v>0.1702536836391225</v>
+        <v>3.055608404780062</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.9683603068768686</v>
+        <v>0.0623754329128906</v>
       </c>
       <c r="C8">
-        <v>0.3466622498137921</v>
+        <v>0.03839730280062771</v>
       </c>
       <c r="D8">
-        <v>-2.793382629337398</v>
+        <v>1.624474334480361</v>
       </c>
       <c r="E8">
-        <v>0.006722210589738653</v>
+        <v>0.1069888083545911</v>
       </c>
       <c r="F8">
-        <v>-1.659756363155589</v>
+        <v>-0.01367526343697811</v>
       </c>
       <c r="G8">
-        <v>-0.2769642505981478</v>
+        <v>0.1384261292627593</v>
       </c>
     </row>
   </sheetData>
